--- a/02_加值成品/八上/八上4-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上4-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上4-1 光的傳播與反射　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二上學期 八上4-1 光的傳播與反射　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>光在均勻介質中如何前進？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>沿直線</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>凹面鏡</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>發散</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>與物等大</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>直進</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>反射定律:入射角等於？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>發散</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>虛像</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>反射角</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>法線</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>相等</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>量入射角以什麼為準？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>沿直線</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>直進</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>月球</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>法線</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>垂直面</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>平面鏡成的像是實像還虛像？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>月球</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>反射角</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>虛像</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>發散</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>鏡後</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>平面鏡像的大小？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>同步增大</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>沿直線</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>倒立實像</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>與物等大</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>1:1</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>平面鏡像左右如何？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>沿直線</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>左右相反</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>月球</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>反射角</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>鏡像</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>會聚光線的面鏡是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>直進</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>反射角</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>凹面鏡</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>虛像</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>聚光</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>影子形成是因為光？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>沿直線</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>直進</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>月球</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>左右相反</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>被擋</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>光遇鏡面返回的現象是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>沿直線</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>與物等大</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>倒立實像</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>反射</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>反射</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>平面鏡成像像距與物距？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>虛像</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>反射角</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>相等</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>發散</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>對稱</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上4-1 光的傳播與反射　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二上學期 八上4-1 光的傳播與反射　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>入射角30°，反射角？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>80°</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>50°</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>0°</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>30°</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>相等</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>物距20cm，平面鏡像距？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>20 cm</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>50°</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>3個</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>0°</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>對稱</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>入射光垂直鏡面，反射角？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>30°</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>50°</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>80°</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>0°</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>原路返回</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>汽車後視鏡多用哪種面鏡？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>沿直線</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>與物等大</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>凸面鏡</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>同步增大</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>視野廣</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>日食是什麼擋住太陽？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>月球</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>發散</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>虛像</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>同步增大</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>光直進</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>入射角40°，入射線與反射線夾角？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>30°</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>0°</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>50°</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>80°</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>40+40</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>太陽灶聚熱用哪種面鏡？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>凹面鏡</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>正立放大虛像</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>月球</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>反射</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>會聚</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>針孔成像的像是？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>虛像</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>凸面鏡</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>凹面鏡</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>倒立實像</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>光直進</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>入射角50°反射角？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>30°</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>0°</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>80°</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>50°</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>相等</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>凸面鏡使光線？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>法線</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>沿直線</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>左右相反</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>發散</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>發散</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上4-1 光的傳播與反射　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二上學期 八上4-1 光的傳播與反射　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何平面鏡成虛像？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>跟著靠近,像距等物距</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>兩面鏡反射光路</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>反射光反向延長交會、非實際會聚</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>兩平面鏡各45°</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>虛像本質</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>潛望鏡用幾面鏡如何擺？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>跟著靠近,像距等物距</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>漫反射方向雜亂</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>地球擋住射向月球的陽光</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>兩平面鏡各45°</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>平行反射</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>人退後1m，平面鏡中像退幾m？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>1 m(像距等物距)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>地球擋住射向月球的陽光</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>漫反射方向雜亂</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>兩面鏡反射光路</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>對稱移動</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>凹面鏡物在焦點內成？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>正立放大虛像</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>虛像</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>左右相反</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>相等</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>如化妝鏡</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>月食是誰擋住誰？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>兩平面鏡各45°</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>地球擋住射向月球的陽光</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>漫反射方向雜亂</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>跟著靠近,像距等物距</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>直進</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>入射角增大反射角如何？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>凹面鏡</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>同步增大</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>凸面鏡</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>反射</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>恆相等</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>鏡面粗糙為何看不到清晰像？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>兩平面鏡各45°</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>地球擋住射向月球的陽光</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>兩面鏡反射光路</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>漫反射方向雜亂</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>表面</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>兩鏡夾90°物體成幾個像？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>3個</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>20 cm</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>30°</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>80°</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>多次反射</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>潛望鏡能看到障礙後方靠什麼？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>1 m(像距等物距)</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>地球擋住射向月球的陽光</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>跟著靠近,像距等物距</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>兩面鏡反射光路</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>反射</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>平面鏡前物體靠近鏡面像如何？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>跟著靠近,像距等物距</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>漫反射方向雜亂</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>反射光反向延長交會、非實際會聚</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>1 m(像距等物距)</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>對稱</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八上/八上4-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上4-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>直進</t>
+          <t>直進：光在同一種均勻介質中傳播時，沒有受到阻礙或介質改變，會沿著直線前進</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>相等</t>
+          <t>相等：光的反射定律指出，反射角一定等於入射角，這是反射現象的基本規則</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>垂直面</t>
+          <t>垂直面：入射角是入射光線和鏡面法線(垂直於鏡面的假想線)之間的夾角，測量時以法線為基準</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>鏡後</t>
+          <t>鏡後：平面鏡的反射光是發散的，眼睛看到的光線反向延長後才會交會在鏡子後方，這種不是真正光線交會而成的像稱為虛像</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>1:1</t>
+          <t>1:1：平面鏡成的虛像大小和物體本身完全相同，比例是1比1</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>鏡像</t>
+          <t>鏡像：平面鏡成像時，前後方向會顛倒過來，看起來就像左右相反的鏡像</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>聚光</t>
+          <t>聚光：凹面鏡向內凹陷，能把平行射入的光線反射會聚到一點，具有聚光的效果</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>被擋</t>
+          <t>被擋：光沿直線前進，遇到不透光的物體被擋住，光無法繼續前進到後方，就形成了影子</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>反射</t>
+          <t>反射：光線照射到鏡面等光滑表面後彈回來的現象稱為反射</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>對稱</t>
+          <t>對稱：平面鏡成像時，像和鏡面的距離(像距)會等於物體和鏡面的距離(物距)，兩者對稱</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>相等</t>
+          <t>相等：根據反射定律，反射角一定等於入射角，入射角30度反射角也是30度</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>對稱</t>
+          <t>對稱：平面鏡成像時像距一定等於物距，物體離鏡面20公分，像也在鏡子後方20公分處</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>原路返回</t>
+          <t>原路返回：光線垂直射入鏡面時，入射角是0度，根據反射定律反射角也是0度，光會沿原路徑反射回去</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>視野廣</t>
+          <t>視野廣：凸面鏡能把光線向外反射發散，成像範圍比平面鏡大，能看到更廣的視野，所以後視鏡常用凸面鏡</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>光直進</t>
+          <t>光直進：日食是月球運行到太陽和地球之間，因為光沿直線前進、被月球擋住，使地球上部分區域看不到太陽</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>40+40</t>
+          <t>40+40：入射角等於反射角都是40度，入射線和反射線之間的夾角是兩者相加，40加40等於80度</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>會聚</t>
+          <t>會聚：凹面鏡能把平行射入的陽光反射會聚到一點，使該處溫度大幅升高，所以太陽灶用凹面鏡聚熱</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>光直進</t>
+          <t>光直進：光沿直線前進，通過小孔後在後方屏幕上交會成像，因為光線交叉，成的像是上下左右顛倒的倒立實像</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>相等</t>
+          <t>相等：根據反射定律，反射角一定等於入射角，入射角50度反射角也是50度</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>發散</t>
+          <t>發散：凸面鏡向外凸出，會把平行射入的光線向外反射發散開來</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>虛像本質</t>
+          <t>虛像本質：平面鏡反射出去的光線本身是發散的，並沒有真正在鏡後交會，只是把反射光線往後反向延長，在假想的交會點看起來像有一個像，這種像稱為虛像</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>平行反射</t>
+          <t>平行反射：潛望鏡內裝有兩片互相平行、各與鏡管成45度角擺放的平面鏡，光線經過兩次反射改變路徑，讓人可以看到障礙物後方的景象</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>對稱移動</t>
+          <t>對稱移動：因為平面鏡像距永遠等於物距，人退後1公尺，鏡中的像也會跟著對稱地退後1公尺</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>如化妝鏡</t>
+          <t>如化妝鏡：當物體放在凹面鏡焦點以內時，會成一個正立、放大的虛像，這正是化妝鏡放大臉部影像的原理</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>直進</t>
+          <t>直進：月食是地球運行到太陽和月球之間，因為光沿直線前進、地球擋住了原本要照到月球的陽光，使月球被地球的影子遮蔽</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>恆相等</t>
+          <t>恆相等：根據反射定律，反射角永遠等於入射角，入射角變大，反射角也會跟著同步變大，兩者維持相等關係</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>表面</t>
+          <t>表面：鏡面如果粗糙不平，光線照射到各個微小凹凸面時會朝各種不同方向反射(漫反射)，反射方向雜亂不一致，無法在特定位置聚集成清晰的像</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>多次反射</t>
+          <t>多次反射：兩面鏡子夾角90度時，光線在兩鏡之間會經過多次反射，物體共會成3個像，夾角越小成像數目通常越多</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>反射</t>
+          <t>反射：潛望鏡內裝有兩面互相平行的鏡子，光線經過兩次反射改變路徑，讓人可以看到原本被障礙物擋住視線後方的景象</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>對稱</t>
+          <t>對稱：因為平面鏡像距永遠等於物距，物體靠近鏡面時，鏡中的像也會跟著等距離靠近鏡面</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八上/八上4-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上4-1_三種難度測驗卷.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>發散</t>
+          <t>法線</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>虛像</t>
+          <t>同步增大</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>法線</t>
+          <t>沿直線</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -683,12 +683,12 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>月球</t>
+          <t>左右相反</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>反射角</t>
+          <t>沿直線</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>發散</t>
+          <t>凸面鏡</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>沿直線</t>
+          <t>直進</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>倒立實像</t>
+          <t>月球</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1039,17 +1039,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
+          <t>3個</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>20 cm</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
           <t>80°</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>50°</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>0°</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -1119,17 +1119,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>30°</t>
+          <t>虛像</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>50°</t>
+          <t>相等</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>80°</t>
+          <t>反射</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
+          <t>3個</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
           <t>30°</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>0°</t>
-        </is>
-      </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>50°</t>
+          <t>20 cm</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -1359,17 +1359,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
+          <t>20 cm</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>3個</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
           <t>30°</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>0°</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>80°</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1640,17 +1640,17 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>虛像</t>
+          <t>與物等大</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>左右相反</t>
+          <t>月球</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>相等</t>
+          <t>沿直線</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
